--- a/data/Hermenches/cost/cost_report.xlsx
+++ b/data/Hermenches/cost/cost_report.xlsx
@@ -482,30 +482,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85.46155629208825</v>
+        <v>87.7346164127494</v>
       </c>
       <c r="C2" t="n">
-        <v>1609.797819514314</v>
+        <v>1919.939378820379</v>
       </c>
       <c r="D2" t="n">
-        <v>2452.336379036293</v>
+        <v>902.0201422778952</v>
       </c>
       <c r="E2" t="n">
-        <v>340.4950218277669</v>
+        <v>916.8171533422656</v>
       </c>
       <c r="F2" t="n">
-        <v>4961.12689673056</v>
+        <v>8012.848064172324</v>
       </c>
       <c r="G2" t="n">
-        <v>9449.217673401021</v>
+        <v>11839.35935502562</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1189494489118132</v>
+        <v>0.148982215081841</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85.23964681781823</v>
+        <v>87.37694928176012</v>
       </c>
       <c r="C3" t="n">
-        <v>1562.546577817204</v>
+        <v>3628.587227396264</v>
       </c>
       <c r="D3" t="n">
-        <v>2585.372004908148</v>
+        <v>-4023.156897879823</v>
       </c>
       <c r="E3" t="n">
-        <v>340.4393112559966</v>
+        <v>1924.485480556701</v>
       </c>
       <c r="F3" t="n">
-        <v>5198.423121279809</v>
+        <v>9359.994047064463</v>
       </c>
       <c r="G3" t="n">
-        <v>9772.020662078976</v>
+        <v>10977.28680641937</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>base</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1230129850623683</v>
+        <v>0.1381342059961053</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86.00274113262819</v>
+        <v>87.37694928176012</v>
       </c>
       <c r="C4" t="n">
-        <v>1062.743805853115</v>
+        <v>3626.002848516887</v>
       </c>
       <c r="D4" t="n">
-        <v>4040.679502138788</v>
+        <v>-3870.026066165092</v>
       </c>
       <c r="E4" t="n">
-        <v>337.9008124833246</v>
+        <v>2100.831012913118</v>
       </c>
       <c r="F4" t="n">
-        <v>4292.33773792207</v>
+        <v>9741.00457562948</v>
       </c>
       <c r="G4" t="n">
-        <v>9819.664599529926</v>
+        <v>11685.18932017615</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1236127405447436</v>
+        <v>0.147042195136305</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.09809013176337</v>
+        <v>87.36809550992629</v>
       </c>
       <c r="C5" t="n">
-        <v>1049.569070933368</v>
+        <v>1933.793011956954</v>
       </c>
       <c r="D5" t="n">
-        <v>4206.715964306967</v>
+        <v>784.1543531938602</v>
       </c>
       <c r="E5" t="n">
-        <v>341.5840179498994</v>
+        <v>880.3084071917076</v>
       </c>
       <c r="F5" t="n">
-        <v>4461.224943905962</v>
+        <v>7593.115209687158</v>
       </c>
       <c r="G5" t="n">
-        <v>10145.19208722796</v>
+        <v>11278.73907753961</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1277105734665447</v>
+        <v>0.1419275723216136</v>
       </c>
     </row>
   </sheetData>

--- a/data/Hermenches/cost/cost_report.xlsx
+++ b/data/Hermenches/cost/cost_report.xlsx
@@ -482,30 +482,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87.7346164127494</v>
+        <v>87.37694928176012</v>
       </c>
       <c r="C2" t="n">
-        <v>1919.939378820379</v>
+        <v>3628.587227396264</v>
       </c>
       <c r="D2" t="n">
-        <v>902.0201422778952</v>
+        <v>-4023.156897879823</v>
       </c>
       <c r="E2" t="n">
-        <v>916.8171533422656</v>
+        <v>1924.485480556701</v>
       </c>
       <c r="F2" t="n">
-        <v>8012.848064172324</v>
+        <v>9359.994047064463</v>
       </c>
       <c r="G2" t="n">
-        <v>11839.35935502562</v>
+        <v>10977.28680641937</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>base</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.148982215081841</v>
+        <v>0.1381342059961053</v>
       </c>
     </row>
     <row r="3">
@@ -518,27 +518,27 @@
         <v>87.37694928176012</v>
       </c>
       <c r="C3" t="n">
-        <v>3628.587227396264</v>
+        <v>3626.002848516887</v>
       </c>
       <c r="D3" t="n">
-        <v>-4023.156897879823</v>
+        <v>-3870.026066165092</v>
       </c>
       <c r="E3" t="n">
-        <v>1924.485480556701</v>
+        <v>2100.831012913118</v>
       </c>
       <c r="F3" t="n">
-        <v>9359.994047064463</v>
+        <v>9741.00457562948</v>
       </c>
       <c r="G3" t="n">
-        <v>10977.28680641937</v>
+        <v>11685.18932017615</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1381342059961053</v>
+        <v>0.147042195136305</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>87.37694928176012</v>
+        <v>87.7346164127494</v>
       </c>
       <c r="C4" t="n">
-        <v>3626.002848516887</v>
+        <v>1919.939378820379</v>
       </c>
       <c r="D4" t="n">
-        <v>-3870.026066165092</v>
+        <v>902.0201422778952</v>
       </c>
       <c r="E4" t="n">
-        <v>2100.831012913118</v>
+        <v>916.8171533422656</v>
       </c>
       <c r="F4" t="n">
-        <v>9741.00457562948</v>
+        <v>8012.848064172324</v>
       </c>
       <c r="G4" t="n">
-        <v>11685.18932017615</v>
+        <v>11839.35935502562</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.147042195136305</v>
+        <v>0.148982215081841</v>
       </c>
     </row>
     <row r="5">

--- a/data/Hermenches/cost/cost_report.xlsx
+++ b/data/Hermenches/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87.37694928176012</v>
+        <v>76.89301584843845</v>
       </c>
       <c r="C2" t="n">
-        <v>3628.587227396264</v>
+        <v>3543.384400864667</v>
       </c>
       <c r="D2" t="n">
-        <v>-4023.156897879823</v>
+        <v>-2406.369679238626</v>
       </c>
       <c r="E2" t="n">
-        <v>1924.485480556701</v>
+        <v>724.8079556709786</v>
       </c>
       <c r="F2" t="n">
-        <v>9359.994047064463</v>
+        <v>8891.239625066148</v>
       </c>
       <c r="G2" t="n">
-        <v>10977.28680641937</v>
+        <v>10829.95531821161</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1381342059961053</v>
+        <v>0.1362802398475756</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87.37694928176012</v>
+        <v>77.06564123256865</v>
       </c>
       <c r="C3" t="n">
-        <v>3626.002848516887</v>
+        <v>3521.355474156387</v>
       </c>
       <c r="D3" t="n">
-        <v>-3870.026066165092</v>
+        <v>-2175.354576637659</v>
       </c>
       <c r="E3" t="n">
-        <v>2100.831012913118</v>
+        <v>815.9071121347971</v>
       </c>
       <c r="F3" t="n">
-        <v>9741.00457562948</v>
+        <v>9170.722878574063</v>
       </c>
       <c r="G3" t="n">
-        <v>11685.18932017615</v>
+        <v>11409.69652946016</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.147042195136305</v>
+        <v>0.1435754935210251</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>87.7346164127494</v>
+        <v>76.81138376441761</v>
       </c>
       <c r="C4" t="n">
-        <v>1919.939378820379</v>
+        <v>1989.745727037921</v>
       </c>
       <c r="D4" t="n">
-        <v>902.0201422778952</v>
+        <v>1687.012268889971</v>
       </c>
       <c r="E4" t="n">
-        <v>916.8171533422656</v>
+        <v>424.974047906237</v>
       </c>
       <c r="F4" t="n">
-        <v>8012.848064172324</v>
+        <v>6913.400109577716</v>
       </c>
       <c r="G4" t="n">
-        <v>11839.35935502562</v>
+        <v>11091.94353717626</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.148982215081841</v>
+        <v>0.1395770048173907</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>87.36809550992629</v>
+        <v>76.98057584242281</v>
       </c>
       <c r="C5" t="n">
-        <v>1933.793011956954</v>
+        <v>1969.753646473853</v>
       </c>
       <c r="D5" t="n">
-        <v>784.1543531938602</v>
+        <v>1879.266115185716</v>
       </c>
       <c r="E5" t="n">
-        <v>880.3084071917076</v>
+        <v>459.5286005460518</v>
       </c>
       <c r="F5" t="n">
-        <v>7593.115209687158</v>
+        <v>7223.442784151385</v>
       </c>
       <c r="G5" t="n">
-        <v>11278.73907753961</v>
+        <v>11608.97172219943</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1419275723216136</v>
+        <v>0.1460831004560705</v>
       </c>
     </row>
   </sheetData>
